--- a/output/2026-09-01_00_Italia_Liguria_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-01_00_Italia_Liguria_Componentistica_Ventilazione_industriale.xlsx
@@ -582,7 +582,6 @@
           <t>010 6504830</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Verificato via paginebianche.it, virgilio.it, sito raelgenova.it. Via Borzoli 46/E, Genova. Titolare: Eleuterio Battistini. Nessuna email pubblica trovata.</t>
@@ -615,11 +614,9 @@
           <t>Aspiratori industriali/professionali (anche fissi), compressori industriali, vendita/noleggio/assistenza</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Verificato via sito gevapor.it. ATTENZIONE - possibile settore adiacente: offerta centrata su aspiratori/aspirapolvere per pulizia industriale e compressori, non su componentistica di ventilazione impiantistica (ventilatori centrifughi/assiali, filtri, dust collector) in senso stretto. Da valutare pertinenza. Telefono/email non trovati nei risultati di ricerca, lasciati vuoti.</t>
+          <t>Verificato via sito gevapor.it. ATTENZIONE - possibile settore adiacente: offerta centrata su aspiratori/aspirapolvere per pulizia industriale e compressori, non su componentistica di ventilazione impiantistica (ventilatori centrifughi/assiali, filtri, dust collector) in senso stretto. Da valutare pertinenza. Telefono/email non trovati nei risultati di ricerca, lasciati vuoti. [DUPLICATO — vedi anche: 2026-08-31_21_Italia_Liguria_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -738,7 +735,6 @@
           <t>010 6592011 / 0187 982128</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Verificato via LinkedIn aziendale e sito bierredi.it. Fondata nel 1980, ISO 9001. Cinque sedi (Genova, Savona, La Spezia, Alessandria, Cuneo). Email non trovata.</t>
@@ -776,10 +772,9 @@
           <t>010 7171456</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Verificato via sito climatique.it. Via Romairone 42/E, Genova. Perfettamente in target (impianti di ventilazione/aspirazione industriale). Telefono trovato in ricerca (diverso da quello indicato come vuoto nella lista originale); email non trovata.</t>
+          <t>Verificato via sito climatique.it. Via Romairone 42/E, Genova. Perfettamente in target (impianti di ventilazione/aspirazione industriale). Telefono trovato in ricerca (diverso da quello indicato come vuoto nella lista originale); email non trovata. [DUPLICATO — vedi anche: 2026-08-31_23_Italia_Liguria_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -821,7 +816,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Verificato via Facebook aziendale e sito ellebisolutions.it. Via Cereghetta 2A, Rapallo.</t>
+          <t>Verificato via Facebook aziendale e sito ellebisolutions.it. Via Cereghetta 2A, Rapallo. [DUPLICATO — vedi anche: 2026-08-31_22_Italia_Liguria_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -863,7 +858,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Verificato via misterimprese.it e sito tubair.it. Ricerca ha mostrato anche un cellulare 335 6894994 del responsabile tecnico Alessandro, in aggiunta al fisso aziendale fornito. In target (produzione condotti per aspirazione industriale).</t>
+          <t>Verificato via misterimprese.it e sito tubair.it. Ricerca ha mostrato anche un cellulare 335 6894994 del responsabile tecnico Alessandro, in aggiunta al fisso aziendale fornito. In target (produzione condotti per aspirazione industriale). [DUPLICATO — vedi anche: 2026-08-31_22_Italia_Liguria_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -940,7 +935,6 @@
           <t>0187 20186 / 721449 / 736893</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Verificato via paginebianche.it, sito aebcuscinettisp.it. Viale Italia 123, La Spezia. Oltre 40 anni di attività. Email non trovata.</t>
@@ -1000,7 +994,6 @@
           <t>Officina Elettromeccanica Pini</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>SV - Savona</t>
@@ -1016,7 +1009,6 @@
           <t>019 824813</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Nessun sito ufficiale rintracciato. Verificato tramite directory (paginebianche.it, misterimprese.it, virgilio.it, officinemeccaniche.it): Via Alessandria 9/R, Savona. Telefono trovato in ricerca (non presente nella lista grezza originale, dove era vuoto) - dato reale da fonte verificabile, non inventato. Email non trovata, lasciata vuota.</t>
